--- a/daily_matches/job_matches_2026-10-15.xlsx
+++ b/daily_matches/job_matches_2026-10-15.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Advanced AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, LangChain, Gemini, Hugging Face, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8166ffe447c83c</t>
+          <t>https://www.indeed.com/viewjob?jk=878b0744411a1f9f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Back-end)</t>
+          <t>Data Engineer 4 - ERM Transformation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mad Mobile</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Git, Kafka</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049e17c22f6357d3</t>
+          <t>https://www.indeed.com/viewjob?jk=15b0331f4e03bd52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GenAI/Python Developer - AI/ML - Newyork, NY - Citi</t>
+          <t>Software Engineer 1 – Full-stack, Generative AI, Cloud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Brookfield, WI, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c525fa32512d4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=30ea3ac63f50ac91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer 1 – Full-stack, Generative AI, Cloud</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oakwood Systems Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, AKS, CI/CD, Git, Databricks</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,67 +589,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8adc70dab60b5264</t>
+          <t>https://www.indeed.com/viewjob?jk=15607638a498d15d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer - Core Platforms</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Hadoop, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee611649ef0f40c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a14e8e38f07dfff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Gemini Enterprise Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oakwood Systems Group</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chandler, AZ, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, AKS, CI/CD, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02af0306e380da94</t>
+          <t>https://www.indeed.com/viewjob?jk=e95908d5d1e5bdc8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Engineer 4 ( Cloud Operations Resilience Engineering) (MEG)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oakwood Systems Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kansas City, MO, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, AKS, CI/CD, Git, Databricks</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,67 +694,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9abf4632add3f574</t>
+          <t>https://www.indeed.com/viewjob?jk=8056429fb51399a8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Automation Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomorrow.io</t>
+          <t>Sanmina</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Golden, CO, USA USA</t>
+          <t>Turtle Lake, WI, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Docker, Kubernetes, Terraform, Git, MongoDB, NoSQL, Matplotlib, Python</t>
+          <t>Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c299784b27caa7</t>
+          <t>https://www.indeed.com/viewjob?jk=89017be06621ecc9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer</t>
+          <t>Sr. Data Scientist - Supply Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Endor Labs</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, USA USA</t>
+          <t>Des Plaines, IL, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, MongoDB, Python, R</t>
+          <t>Data Scientist, Generative AI, Data Lake, CI/CD, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c7e1fd779e75aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0b651969a7309572</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Business Analytics Engineer Enterprise - Oahu</t>
+          <t>Sr. Data Analyst - Tableau Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hawaiian Electric Company, Inc.</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Honolulu, HI, USA USA</t>
+          <t>Albany, NY, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,392 +799,147 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b8c018503ce6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1502481dfd3e282</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer II (US)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Ascend Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, USA USA</t>
+          <t>Boulder, CO, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, MySQL, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, CI/CD, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15141184b12f52a</t>
+          <t>https://www.indeed.com/viewjob?jk=d70f4ba9ab0e6937</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI-Native Software Engineer - Consultant</t>
+          <t>Data Engineer II (Full Time) - United States</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XPRIZE Foundation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Research Triangle Park, NC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, Git, Hadoop, PostgreSQL, MySQL, MongoDB, Tableau, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e15c410c50fa30</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ad2f1353c84509</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agentic AI Infrastructure Engineer II - Core Platforms</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Davidson, NC, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, MySQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991e515999a78167</t>
+          <t>https://www.indeed.com/viewjob?jk=635a32433709351a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Nespresso</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7d9604432fc69</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer - Security &amp; Trust</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Truveta</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=413630bf00116978</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Goodwin Procter LLP</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f385f431c05e95eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ML Engineer, Agentic Systems</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Viridien</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Houston, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67febc962942f43e</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Verizon</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a8a3060e238344</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ALTANA AG</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, Docker, Kubernetes, Git, Databricks, PySpark, Python, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3f63c42f2039db</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Revenue Data Analyst</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Hertz</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Estero, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, PySpark, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=048b033996f3ea64</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Google Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Slalom Consulting</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98ee560b6b53530b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1958d789cfe471</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-15.xlsx
+++ b/daily_matches/job_matches_2026-10-15.xlsx
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Advanced AI Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Gemini, Hugging Face, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878b0744411a1f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a8059421c16401</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - ERM Transformation</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b0331f4e03bd52</t>
+          <t>https://www.indeed.com/viewjob?jk=d0cd3bb4e3adcf71</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer 1 – Full-stack, Generative AI, Cloud</t>
+          <t>Software Power Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Electric Power Engineers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brookfield, WI, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Polars, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ea3ac63f50ac91</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9115fc0835130e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer 1 – Full-stack, Generative AI, Cloud</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15607638a498d15d</t>
+          <t>https://www.indeed.com/viewjob?jk=631de39f772a7e57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a14e8e38f07dfff</t>
+          <t>https://www.indeed.com/viewjob?jk=2b363a6b62d7ea4b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Gemini Enterprise Engineer</t>
+          <t>SRE - DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chandler, AZ, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95908d5d1e5bdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed982ec7d62db1ac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer 4 ( Cloud Operations Resilience Engineering) (MEG)</t>
+          <t>Autonomy Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8056429fb51399a8</t>
+          <t>https://www.indeed.com/viewjob?jk=231e3a6ce9aee2e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Automation Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sanmina</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turtle Lake, WI, USA USA</t>
+          <t>Ithaca, NY, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, C++</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89017be06621ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=29614a86942ce0a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist - Supply Chain</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>US Foods</t>
+          <t>TicketManager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, USA USA</t>
+          <t>Calabasas, CA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Data Lake, CI/CD, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, Gemini, Prompt Engineering, Data Lake, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b651969a7309572</t>
+          <t>https://www.indeed.com/viewjob?jk=46dd990f11dd31b3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Albany, NY, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, Gemini, Docker, CI/CD, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1502481dfd3e282</t>
+          <t>https://www.indeed.com/viewjob?jk=66bd1d89e8bb9513</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>AI Engineer--Office Based Raleigh North Carolina</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ascend Analytics</t>
+          <t>CliniSys</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boulder, CO, USA USA</t>
+          <t>Morrisville, NC, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70f4ba9ab0e6937</t>
+          <t>https://www.indeed.com/viewjob?jk=084c481d99128d48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II (Full Time) - United States</t>
+          <t>AI Solutions Engineer (ITS Architect III)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, USA USA</t>
+          <t>Orange, CA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Git, Hadoop, PostgreSQL, MySQL, MongoDB, Tableau, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ad2f1353c84509</t>
+          <t>https://www.indeed.com/viewjob?jk=5734570abad75e05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Davidson, NC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,19 +904,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a32433709351a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8bb619012d55a29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Hybrid)</t>
+          <t>Senior BI Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nespresso</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>S3, Glue, Athena, CI/CD, Tableau, Quicksight, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1958d789cfe471</t>
+          <t>https://www.indeed.com/viewjob?jk=cce3223e9c173979</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-15.xlsx
+++ b/daily_matches/job_matches_2026-10-15.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI / ML Ops Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>AK, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a8059421c16401</t>
+          <t>https://www.indeed.com/viewjob?jk=d731eb5827ed8c1a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Lake Forest, IL, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cd3bb4e3adcf71</t>
+          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Power Systems Engineer</t>
+          <t>Data &amp; AI Engineer, Advanced</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electric Power Engineers</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Niskayuna, NY, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Polars, Python, SQL, R, Java</t>
+          <t>AI Engineer, Copilot, Azure ML, Synapse, Data Lake, CI/CD, Git, Snowflake, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9115fc0835130e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a1ff9a7450560f5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI and Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arizona Cardinals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, PyTorch, MLflow</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Glue, Data Lake, Databricks, Power BI, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631de39f772a7e57</t>
+          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b363a6b62d7ea4b</t>
+          <t>https://www.indeed.com/viewjob?jk=aefdba2451cecaee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRE - DevOps Engineer</t>
+          <t>Full Stack Engineer- Cascadience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VIABILITY, INC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Springfield, MA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
+          <t>LangChain, RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed982ec7d62db1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=18666d76e51446f5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Autonomy Engineer</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
+          <t>Generative AI, RAG, FastAPI, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231e3a6ce9aee2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c32423a07be0d07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Analytics Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Proper Hospitality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ithaca, NY, USA USA</t>
+          <t>Santa Monica, CA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29614a86942ce0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9155639e76e6a19f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TicketManager</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Calabasas, CA, USA USA</t>
+          <t>Minnetonka, MN, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Data Lake, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, S3, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46dd990f11dd31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3f81a03c207b40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Part time Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>GeoVisual Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Gemini, Docker, CI/CD, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, PyTorch, FastAPI, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bd1d89e8bb9513</t>
+          <t>https://www.indeed.com/viewjob?jk=e946bc71de41def8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer--Office Based Raleigh North Carolina</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CliniSys</t>
+          <t>Umain</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morrisville, NC, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084c481d99128d48</t>
+          <t>https://www.indeed.com/viewjob?jk=751162fb1ff8490a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer (ITS Architect III)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orange, CA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Databricks, Python, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Snowflake, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5734570abad75e05</t>
+          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Co-op- Robot Manipulation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Wilmington, MA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Databricks, Python, R, Scala</t>
+          <t>RAG, OpenCV, Docker, CI/CD, Jenkins, Git, Python, R, C++, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,42 +904,147 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8bb619012d55a29</t>
+          <t>https://www.indeed.com/viewjob?jk=b10a1eda50b51a21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior BI Platform Operations Engineer</t>
+          <t>Senior Associate, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9e726e5fe8044bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer – Startups &amp; Partnerships</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>S3, Glue, Athena, CI/CD, Tableau, Quicksight, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cce3223e9c173979</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Git, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e426807d6c91f8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Northborough, MA, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9320ce716532f4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Perception Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Apptronik</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Python, R, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59ef59c74d5dafa5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-15.xlsx
+++ b/daily_matches/job_matches_2026-10-15.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI / ML Ops Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Children's Healthcare of Atlanta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, USA USA</t>
+          <t>Brookhaven, GA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Git, BigQuery</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, Azure ML, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d731eb5827ed8c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2dab3ac5d3446af2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Georgia Ports Authority</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, USA USA</t>
+          <t>Savannah, GA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, Databricks, NoSQL, Python</t>
+          <t>AI Engineer, Copilot, TensorFlow, PyTorch, scikit-learn, BigQuery, CI/CD, Git, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer, Advanced</t>
+          <t>Analyst – Data Products and AI Enablement</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Azure ML, Synapse, Data Lake, CI/CD, Git, Snowflake, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Cortex, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a1ff9a7450560f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI and Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arizona Cardinals</t>
+          <t>Curium Pharmaceuticals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Glue, Data Lake, Databricks, Power BI, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
+          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. QA Test Engineer (Quality Assurance)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, PyTorch, MLflow</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Glue, Redshift, Data Lake, CI/CD, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefdba2451cecaee</t>
+          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer- Cascadience</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VIABILITY, INC</t>
+          <t>Invid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Springfield, MA, USA USA</t>
+          <t>San Juan, PR, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Redshift, Hadoop, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18666d76e51446f5</t>
+          <t>https://www.indeed.com/viewjob?jk=760ec267ea1992e9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, BigQuery, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c32423a07be0d07</t>
+          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Data Platform</t>
+          <t>Data &amp; AI Engineer, Advanced</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Proper Hospitality</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, USA USA</t>
+          <t>Niskayuna, NY, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Copilot, Azure ML, Synapse, Data Lake, CI/CD, Git, Snowflake, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9155639e76e6a19f</t>
+          <t>https://www.indeed.com/viewjob?jk=1121cabf48789bf1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Data and AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, S3, CI/CD, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3f81a03c207b40</t>
+          <t>https://www.indeed.com/viewjob?jk=203bb719c5957421</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Part time Sr. Software Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GeoVisual Analytics</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, PyTorch, FastAPI, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, Snowflake, PostgreSQL, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e946bc71de41def8</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Umain</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, R, Java, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751162fb1ff8490a</t>
+          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Snowflake, Kafka, SQL, R, Java</t>
+          <t>Prompt Engineering, Docker, Kubernetes, AKS, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
+          <t>https://www.indeed.com/viewjob?jk=ffa06e20e0c7d2af</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Co-op- Robot Manipulation</t>
+          <t>Sr. AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Post Holdings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, MA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, OpenCV, Docker, CI/CD, Jenkins, Git, Python, R, C++, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, CI/CD, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10a1eda50b51a21</t>
+          <t>https://www.indeed.com/viewjob?jk=79774af1195da56e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Associate, Full-Stack Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e726e5fe8044bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer – Startups &amp; Partnerships</t>
+          <t>Senior Front-End and Agentic-UI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Git, R</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e426807d6c91f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd206950124436f5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Disney Entertainment and ESPN Product &amp; Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northborough, MA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,42 +1009,602 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9320ce716532f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c82a59ee8464deac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Perception Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>WEIDMANN Electrical Technology, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Urbana, OH, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, scikit-learn, Git, Python, R, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9a3071b52405b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer I</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PyTorch, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c40e5a35bad5f64a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - ML Infrastructure</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Claryo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Python, R, C++, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a42c7b65e2610347</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Embedded Software DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RFA Engineering</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Waterloo, IA, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, C++, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6cd878e0c78b044</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elyon International</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Washington, DC, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, Data Lake, CI/CD, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f37a2df21bae7809</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Developer, Implementations</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XiFin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Charleston, SC, USA USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf52f7a4ef4ec7c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Specialist Solution Engineer – Analytics (Tableau)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bb21996f558e93a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Richmond, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Kafka, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6388c10d1d2b151a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DigiCert</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35614edd44e7e984</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Applied AI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Python, R, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef59c74d5dafa5</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LangChain, BigQuery, FastAPI, Git, BigQuery, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8d70d968c65fbff</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr AI Software Security Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Evolent</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, CI/CD, Jenkins, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d911785e83d8936f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Java Developer with Agentic AI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All IT Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59fdc283a2bbc6b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bob Loquercio Auto Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Gemini, BigQuery, Data Lake, Snowflake, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae9ac941bd34be93</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Manufacturing Analytics and Machine Learning Research Assistant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bowling Green State University</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bowling Green, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, XGBoost, LightGBM, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7773562502f07a00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hendrick Automotive Group</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed8d46391a35fde4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist Senior Associate</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Columbus, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53e897732e15b6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Concord, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, Git, MongoDB, Cassandra, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f167e92bd07261c1</t>
         </is>
       </c>
     </row>
